--- a/extra/report/No.課題1_テスト結果.xlsx.xlsx
+++ b/extra/report/No.課題1_テスト結果.xlsx.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D276B30-F904-4E34-BF82-FB09C5AD22B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDFA799-AD3D-475A-9631-BDC920D58560}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>1.トップ画面からログアウトを押下</t>
     <rPh sb="5" eb="7">
@@ -70,6 +70,26 @@
   </si>
   <si>
     <t>2025/07/01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※ログインページではログアウト機能が表示されないことを確認</t>
+    <rPh sb="15" eb="17">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログアウトが表示されなければOK</t>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -136,206 +156,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>65315</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>84364</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9404262B-E696-4AA8-B9DF-6E264FADBB28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="277586" y="696686"/>
-          <a:ext cx="10058400" cy="5657849"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>65316</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>24492</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9125DB4-5A05-4728-A68B-08F15E5D91CB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="277587" y="6906986"/>
-          <a:ext cx="10058400" cy="5657849"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>65315</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>84363</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECB98953-3F07-4EA2-A634-7D498E372BE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="277586" y="13062857"/>
-          <a:ext cx="10058400" cy="5657849"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>65315</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>84364</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F134CA-45E3-44FC-97CD-6F4B68241FD5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="277586" y="19333029"/>
-          <a:ext cx="10058400" cy="5657849"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>35</xdr:col>
@@ -451,6 +271,452 @@
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>65315</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>84363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{520D1F1D-086C-4464-8E84-64D2A367FADB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277586" y="522514"/>
+          <a:ext cx="10058400" cy="5657849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>65315</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4FA485-85A3-4020-8AE4-BB19CA35C94B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277586" y="6792686"/>
+          <a:ext cx="10058400" cy="5657849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>277585</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>168729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>65314</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>78921</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C2DF3B-A7E8-4EB5-B19E-509F3AADEFD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277585" y="13057415"/>
+          <a:ext cx="10058400" cy="5657849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>65315</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>84363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811B0FAB-4DB4-4533-81A2-5192A870E48C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277586" y="19158857"/>
+          <a:ext cx="10058400" cy="5657849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>65315</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B247BA62-8F2D-43B7-9821-1ACF15E8855D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277586" y="25080686"/>
+          <a:ext cx="10058400" cy="5657849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>43543</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>27215</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>21770</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="矢印: 上 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8F8A9A1-7D05-4F71-AA93-C4C74CB1A7D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9906000" y="13628914"/>
+          <a:ext cx="391886" cy="849085"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>168729</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>59870</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>5444</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38098</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="矢印: 上 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B672DD27-93D7-4527-9EF3-3F784131AFC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9884229" y="1104899"/>
+          <a:ext cx="391886" cy="849085"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>168729</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7915101-463B-42F2-A5EC-45CBFECC6022}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9350829" y="25260300"/>
+          <a:ext cx="1191985" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -788,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:AM149"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="52" width="3.625" customWidth="1"/>
@@ -824,6 +1090,16 @@
         <v>3</v>
       </c>
     </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A144" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="39:39" x14ac:dyDescent="0.15">
+      <c r="AM149" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -833,21 +1109,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -1005,31 +1266,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1045,4 +1297,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>